--- a/src/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0018719410415698968</v>
       </c>
       <c r="B2">
-        <v>0.0022313090002110763</v>
+        <v>0.0019542617260587319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0037438820831397937</v>
       </c>
       <c r="B3">
-        <v>0.0035500655500175114</v>
+        <v>0.0031681895775372529</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0056158231247096912</v>
       </c>
       <c r="B4">
-        <v>0.0046990411950015437</v>
+        <v>0.0042362973695254649</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0074877641662795874</v>
       </c>
       <c r="B5">
-        <v>0.0057207569600692173</v>
+        <v>0.0051928695863465062</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0093597052078494836</v>
       </c>
       <c r="B6">
-        <v>0.00663320512327583</v>
+        <v>0.0060525429336008288</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.011231646249419382</v>
       </c>
       <c r="B7">
-        <v>0.0074470249314677094</v>
+        <v>0.0068240429528332478</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.013103587290989278</v>
       </c>
       <c r="B8">
-        <v>0.0081688391966045978</v>
+        <v>0.0075128688340439674</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.014975528332559175</v>
       </c>
       <c r="B9">
-        <v>0.0088083117825652826</v>
+        <v>0.00812692524343384</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.016847469374129072</v>
       </c>
       <c r="B10">
-        <v>0.009375747687167417</v>
+        <v>0.0086746173797222631</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.018719410415698967</v>
       </c>
       <c r="B11">
-        <v>0.0098809753920651062</v>
+        <v>0.0091639470955021726</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.020591351457268866</v>
       </c>
       <c r="B12">
-        <v>0.010329507611699304</v>
+        <v>0.0095994532689717624</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.022463292498838765</v>
       </c>
       <c r="B13">
-        <v>0.010710070507821924</v>
+        <v>0.0099722262268767334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B14">
-        <v>0.0110160899130615</v>
+        <v>0.010277106603877638</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.026207174581978555</v>
       </c>
       <c r="B15">
-        <v>0.011276576896242055</v>
+        <v>0.010537384817746933</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.028079115623548451</v>
       </c>
       <c r="B16">
-        <v>0.011518135986151904</v>
+        <v>0.010774418443075124</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.029951056665118349</v>
       </c>
       <c r="B17">
-        <v>0.011722160315240983</v>
+        <v>0.010973383898613028</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.031822997706688248</v>
       </c>
       <c r="B18">
-        <v>0.011864489591909267</v>
+        <v>0.011115005768961491</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.033694938748258144</v>
       </c>
       <c r="B19">
-        <v>0.011943961224695236</v>
+        <v>0.0111983824579612</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.035566879789828039</v>
       </c>
       <c r="B20">
-        <v>0.01196516204717199</v>
+        <v>0.011227205824262796</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.037438820831397934</v>
       </c>
       <c r="B21">
-        <v>0.01193267889291264</v>
+        <v>0.011205167726516915</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.03931076187296783</v>
       </c>
       <c r="B22">
-        <v>0.011850265781346323</v>
+        <v>0.011135286464595433</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.041182702914537732</v>
       </c>
       <c r="B23">
-        <v>0.011718345475326327</v>
+        <v>0.011017886103255149</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.043054643956107627</v>
       </c>
       <c r="B24">
-        <v>0.011536507923561973</v>
+        <v>0.010852617148474096</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.044926584997677529</v>
       </c>
       <c r="B25">
-        <v>0.011304343074762583</v>
+        <v>0.010639130106230304</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.046798526039247418</v>
       </c>
       <c r="B26">
-        <v>0.011021273074571833</v>
+        <v>0.010376933839817285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B27">
-        <v>0.01068604885637079</v>
+        <v>0.010064970641790441</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.050542408122387215</v>
       </c>
       <c r="B28">
-        <v>0.010297253550474884</v>
+        <v>0.00970204116202066</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.052414349163957111</v>
       </c>
       <c r="B29">
-        <v>0.0098534702871995363</v>
+        <v>0.0092869460503788217</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.054286290205527013</v>
       </c>
       <c r="B30">
-        <v>0.0093538333157302585</v>
+        <v>0.0088189182541469277</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.0561582312470969</v>
       </c>
       <c r="B31">
-        <v>0.00879968136073291</v>
+        <v>0.0082989199102514247</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.0580301722886668</v>
       </c>
       <c r="B32">
-        <v>0.0081929042657434264</v>
+        <v>0.0077283454530298664</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.0599021133302367</v>
       </c>
       <c r="B33">
-        <v>0.007535391874297752</v>
+        <v>0.0071085893168198163</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.061774054371806594</v>
       </c>
       <c r="B34">
-        <v>0.00682801726221647</v>
+        <v>0.0064402209018050265</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.0636459954133765</v>
       </c>
       <c r="B35">
-        <v>0.0060675864344587258</v>
+        <v>0.0057205094715540323</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.065517936454946385</v>
       </c>
       <c r="B36">
-        <v>0.0052498886282683118</v>
+        <v>0.0049458992554815622</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.067389877496516287</v>
       </c>
       <c r="B37">
-        <v>0.0043707130808890073</v>
+        <v>0.0041128344830023379</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.069261818538086176</v>
       </c>
       <c r="B38">
-        <v>0.0034234268698090002</v>
+        <v>0.0032158075957605834</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.071133759579656078</v>
       </c>
       <c r="B39">
-        <v>0.0023917084334940551</v>
+        <v>0.0022415038843184867</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.07300570062122598</v>
       </c>
       <c r="B40">
-        <v>0.0012568140506543329</v>
+        <v>0.0011746568514677297</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.074877641662795869</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>-2.5978400563646208E-19</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.07300570062122598</v>
       </c>
       <c r="B43">
-        <v>0.00043524205878830427</v>
+        <v>0.00051739925797490715</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.071133759579656078</v>
       </c>
       <c r="B44">
-        <v>0.00088966294173837255</v>
+        <v>0.0010398674909139409</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.069261818538086176</v>
       </c>
       <c r="B45">
-        <v>0.0013472341293248335</v>
+        <v>0.0015548534033732503</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.067389877496516287</v>
       </c>
       <c r="B46">
-        <v>0.0017919271020223179</v>
+        <v>0.0020498056999089867</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.065517936454946385</v>
       </c>
       <c r="B47">
-        <v>0.0022099949004008197</v>
+        <v>0.0025139842731875693</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.0636459954133765</v>
       </c>
       <c r="B48">
-        <v>0.0025968168054117877</v>
+        <v>0.002943893768316482</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.061774054371806594</v>
       </c>
       <c r="B49">
-        <v>0.00295005365810204</v>
+        <v>0.0033378500185134831</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.0599021133302367</v>
       </c>
       <c r="B50">
-        <v>0.0032673662995183878</v>
+        <v>0.0036941688569963244</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.0580301722886668</v>
       </c>
       <c r="B51">
-        <v>0.0035473161386078231</v>
+        <v>0.004011874951321384</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.0561582312470969</v>
       </c>
       <c r="B52">
-        <v>0.00379206685591805</v>
+        <v>0.0042928283063995362</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.054286290205527013</v>
       </c>
       <c r="B53">
-        <v>0.0040046826998969484</v>
+        <v>0.00453959776148028</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.052414349163957111</v>
       </c>
       <c r="B54">
-        <v>0.0041882279189924022</v>
+        <v>0.0047547521558131151</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.050542408122387215</v>
       </c>
       <c r="B55">
-        <v>0.0043451296659326412</v>
+        <v>0.0049403420543868651</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B56">
-        <v>0.004475266710567298</v>
+        <v>0.0050963449251476469</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.046798526039247418</v>
       </c>
       <c r="B57">
-        <v>0.0045778807270263561</v>
+        <v>0.0052222199617809042</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.044926584997677529</v>
       </c>
       <c r="B58">
-        <v>0.0046522133894397986</v>
+        <v>0.0053174263579720774</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.043054643956107627</v>
       </c>
       <c r="B59">
-        <v>0.0046976001726832068</v>
+        <v>0.0053814909477710839</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.041182702914537732</v>
       </c>
       <c r="B60">
-        <v>0.004713751754614557</v>
+        <v>0.0054142111266857343</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.03931076187296783</v>
       </c>
       <c r="B61">
-        <v>0.0047004726138374277</v>
+        <v>0.0054154519305883173</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.037438820831397934</v>
       </c>
       <c r="B62">
-        <v>0.0046575672289553924</v>
+        <v>0.005385078395351117</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.035566879789828039</v>
       </c>
       <c r="B63">
-        <v>0.004585599818080024</v>
+        <v>0.00532355604098922</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.033694938748258144</v>
       </c>
       <c r="B64">
-        <v>0.0044881735573548713</v>
+        <v>0.005233752324088908</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.031822997706688248</v>
       </c>
       <c r="B65">
-        <v>0.004369651362431482</v>
+        <v>0.0051191351853792592</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.029951056665118349</v>
       </c>
       <c r="B66">
-        <v>0.0042343961489613976</v>
+        <v>0.0049831725655893559</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.028079115623548451</v>
       </c>
       <c r="B67">
-        <v>0.0040809605553841057</v>
+        <v>0.0048246780984608851</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.026207174581978555</v>
       </c>
       <c r="B68">
-        <v>0.0038846561112908457</v>
+        <v>0.0046238481897859672</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B69">
-        <v>0.0036262568212229078</v>
+        <v>0.0043652401304067664</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.022463292498838765</v>
       </c>
       <c r="B70">
-        <v>0.0033316276983700183</v>
+        <v>0.0040694719793152086</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.020591351457268866</v>
       </c>
       <c r="B71">
-        <v>0.003028964184423894</v>
+        <v>0.0037590185271514352</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.018719410415698967</v>
       </c>
       <c r="B72">
-        <v>0.0027106924264357732</v>
+        <v>0.0034277207229987065</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.016847469374129072</v>
       </c>
       <c r="B73">
-        <v>0.00236444461271588</v>
+        <v>0.0030655749201610339</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.014975528332559175</v>
       </c>
       <c r="B74">
-        <v>0.0019944463912508576</v>
+        <v>0.0026758329303823007</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.013103587290989278</v>
       </c>
       <c r="B75">
-        <v>0.0016091355709982882</v>
+        <v>0.0022651059335589193</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.011231646249419382</v>
       </c>
       <c r="B76">
-        <v>0.0012172051451230924</v>
+        <v>0.0018401871237575542</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0093597052078494836</v>
       </c>
       <c r="B77">
-        <v>0.00082658322652580927</v>
+        <v>0.0014072454162008113</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0074877641662795874</v>
       </c>
       <c r="B78">
-        <v>0.00044188322284210855</v>
+        <v>0.00096977059656481947</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0056158231247096912</v>
       </c>
       <c r="B79">
-        <v>7.1602940240758376E-05</v>
+        <v>0.000534346765716837</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0037438820831397937</v>
       </c>
       <c r="B80">
-        <v>-0.00026869417478507708</v>
+        <v>0.00011318179769518164</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0018719410415698968</v>
       </c>
       <c r="B81">
-        <v>-0.00053916374131237059</v>
+        <v>-0.000262116467160026</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.002175666560754054</v>
       </c>
       <c r="B2">
-        <v>0.00095135953070963253</v>
+        <v>0.00079036020521383251</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.004351333121508108</v>
       </c>
       <c r="B3">
-        <v>0.0014863438831397393</v>
+        <v>0.0012644258939428256</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0065269996822621629</v>
       </c>
       <c r="B4">
-        <v>0.0019496252431570689</v>
+        <v>0.001680712856247868</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0087026662430162161</v>
       </c>
       <c r="B5">
-        <v>0.0023603933529100242</v>
+        <v>0.0020536243678437025</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.01087833280377027</v>
       </c>
       <c r="B6">
-        <v>0.0027264895881504467</v>
+        <v>0.0023890517946741504</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.013053999364524326</v>
       </c>
       <c r="B7">
-        <v>0.0030524004399601658</v>
+        <v>0.0026903695242506908</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.01522966592527838</v>
       </c>
       <c r="B8">
-        <v>0.0033407742201988122</v>
+        <v>0.0029595729026957824</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.017405332486032432</v>
       </c>
       <c r="B9">
-        <v>0.0035957330604518014</v>
+        <v>0.0031997617463945635</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.019580999046786486</v>
       </c>
       <c r="B10">
-        <v>0.00382172418137534</v>
+        <v>0.0034142792536867154</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.02175666560754054</v>
       </c>
       <c r="B11">
-        <v>0.0040230213401830188</v>
+        <v>0.0036063376804674023</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.023932332168294598</v>
       </c>
       <c r="B12">
-        <v>0.0042019143082661775</v>
+        <v>0.0037776608767388889</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.026107998729048652</v>
       </c>
       <c r="B13">
-        <v>0.004352930377169776</v>
+        <v>0.0039241500113763664</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.028283665289802702</v>
       </c>
       <c r="B14">
-        <v>0.00447280193412917</v>
+        <v>0.0040433596496119361</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.03045933185055676</v>
       </c>
       <c r="B15">
-        <v>0.004574844228987694</v>
+        <v>0.0041452806232324139</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.03263499841131081</v>
       </c>
       <c r="B16">
-        <v>0.0046712699226090339</v>
+        <v>0.0042390764525194755</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.034810664972064864</v>
       </c>
       <c r="B17">
-        <v>0.0047532984573303138</v>
+        <v>0.0043181651451795018</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.036986331532818925</v>
       </c>
       <c r="B18">
-        <v>0.0048095866891659112</v>
+        <v>0.004374042284934548</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.039161998093572972</v>
       </c>
       <c r="B19">
-        <v>0.004839534347365791</v>
+        <v>0.0044062592721446463</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.041337664654327026</v>
       </c>
       <c r="B20">
-        <v>0.0048452268794888093</v>
+        <v>0.0044163814613293207</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.04351333121508108</v>
       </c>
       <c r="B21">
-        <v>0.0048287497330938255</v>
+        <v>0.0044059742070080982</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.045688997775835134</v>
       </c>
       <c r="B22">
-        <v>0.0047918165062596219</v>
+        <v>0.0043763235616257647</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.047864664336589195</v>
       </c>
       <c r="B23">
-        <v>0.0047346533991446775</v>
+        <v>0.0043275983693281473</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.050040330897343249</v>
       </c>
       <c r="B24">
-        <v>0.0046571147624273985</v>
+        <v>0.0042596881721863331</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.0522159974580973</v>
       </c>
       <c r="B25">
-        <v>0.00455905494678619</v>
+        <v>0.00417248251227141</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.05439166401885135</v>
       </c>
       <c r="B26">
-        <v>0.0044402658882328827</v>
+        <v>0.0040658237194609289</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.056567330579605404</v>
       </c>
       <c r="B27">
-        <v>0.0043002898641130039</v>
+        <v>0.0039393652748582943</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.058742997140359465</v>
       </c>
       <c r="B28">
-        <v>0.004138606737105509</v>
+        <v>0.003792713447373378</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.060918663701113519</v>
       </c>
       <c r="B29">
-        <v>0.0039546963698893524</v>
+        <v>0.0036254745059160491</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.063094330261867573</v>
       </c>
       <c r="B30">
-        <v>0.00374831318769676</v>
+        <v>0.0034374602317311879</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.06526999682262162</v>
       </c>
       <c r="B31">
-        <v>0.0035203098659730573</v>
+        <v>0.003229304455403724</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.067445663383375681</v>
       </c>
       <c r="B32">
-        <v>0.0032718136427168378</v>
+        <v>0.0030018465198535936</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.069621329944129728</v>
       </c>
       <c r="B33">
-        <v>0.0030039517559266988</v>
+        <v>0.0027559257680007366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.071796996504883789</v>
       </c>
       <c r="B34">
-        <v>0.0027174040175084995</v>
+        <v>0.0024920455379963125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.07397266306563785</v>
       </c>
       <c r="B35">
-        <v>0.00241106053499715</v>
+        <v>0.0022093651489163645</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.0761483296263919</v>
       </c>
       <c r="B36">
-        <v>0.0020833639898348248</v>
+        <v>0.0019067079150681581</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.078323996187145944</v>
       </c>
       <c r="B37">
-        <v>0.0017327570634636945</v>
+        <v>0.0015828971507589554</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0804996627479</v>
       </c>
       <c r="B38">
-        <v>0.0013565874502207056</v>
+        <v>0.0012359345284982495</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.082675329308654052</v>
       </c>
       <c r="B39">
-        <v>0.00094782289602189391</v>
+        <v>0.00086053515360444129</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.084850995869408113</v>
       </c>
       <c r="B40">
-        <v>0.00049833615967806791</v>
+        <v>0.00045059248959816077</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.087026662430162161</v>
       </c>
       <c r="B41">
-        <v>3.8647601754498844E-17</v>
+        <v>3.8798568948852355E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.087026662430162161</v>
       </c>
       <c r="B42">
-        <v>3.8609859955910466E-17</v>
+        <v>3.8647601754498844E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.084850995869408113</v>
       </c>
       <c r="B43">
-        <v>0.00011638679903881045</v>
+        <v>0.00016413046911871766</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.082675329308654052</v>
       </c>
       <c r="B44">
-        <v>0.00024952095668227407</v>
+        <v>0.00033680869909972653</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0804996627479</v>
       </c>
       <c r="B45">
-        <v>0.00039136407644105536</v>
+        <v>0.0005120169981635116</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.078323996187145944</v>
       </c>
       <c r="B46">
-        <v>0.00053387776182578083</v>
+        <v>0.00068373767453052</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.0761483296263919</v>
       </c>
       <c r="B47">
-        <v>0.00067011539170148862</v>
+        <v>0.00084677146646815562</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.07397266306563785</v>
       </c>
       <c r="B48">
-        <v>0.000797497446350863</v>
+        <v>0.00099919283243164888</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.071796996504883789</v>
       </c>
       <c r="B49">
-        <v>0.00091453618141100186</v>
+        <v>0.0011398946609231892</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.069621329944129728</v>
       </c>
       <c r="B50">
-        <v>0.0010197438525190012</v>
+        <v>0.0012677698404449634</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.067445663383375681</v>
       </c>
       <c r="B51">
-        <v>0.0011120766598108854</v>
+        <v>0.0013820437826741294</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.06526999682262162</v>
       </c>
       <c r="B52">
-        <v>0.0011922665814183911</v>
+        <v>0.0014832719919877246</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.063094330261867573</v>
       </c>
       <c r="B53">
-        <v>0.0012614895399721826</v>
+        <v>0.0015723424959377551</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.060918663701113519</v>
       </c>
       <c r="B54">
-        <v>0.0013209214581029252</v>
+        <v>0.0016501433220762289</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.058742997140359465</v>
       </c>
       <c r="B55">
-        <v>0.001371460419248459</v>
+        <v>0.0017173537089805906</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.056567330579605404</v>
       </c>
       <c r="B56">
-        <v>0.0014128931500753277</v>
+        <v>0.0017738177393300373</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.05439166401885135</v>
       </c>
       <c r="B57">
-        <v>0.0014447285380572508</v>
+        <v>0.0018191707068292054</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.0522159974580973</v>
       </c>
       <c r="B58">
-        <v>0.0014664754706679487</v>
+        <v>0.0018530479051827292</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.050040330897343249</v>
       </c>
       <c r="B59">
-        <v>0.0014777020404988768</v>
+        <v>0.001875128630739942</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.047864664336589195</v>
       </c>
       <c r="B60">
-        <v>0.0014782131606124367</v>
+        <v>0.0018852681904289669</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.045688997775835134</v>
       </c>
       <c r="B61">
-        <v>0.0014678729491887667</v>
+        <v>0.0018833658938226235</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.04351333121508108</v>
       </c>
       <c r="B62">
-        <v>0.0014465455244080038</v>
+        <v>0.0018693210504937318</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.041337664654327026</v>
       </c>
       <c r="B63">
-        <v>0.0014144635342128967</v>
+        <v>0.0018433089523723861</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.039161998093572972</v>
       </c>
       <c r="B64">
-        <v>0.0013733337455966329</v>
+        <v>0.0018066088208177778</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.036986331532818925</v>
       </c>
       <c r="B65">
-        <v>0.0013252314553150102</v>
+        <v>0.0017607758595463729</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.034810664972064864</v>
       </c>
       <c r="B66">
-        <v>0.0012722319601238266</v>
+        <v>0.0017073652722746375</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.03263499841131081</v>
       </c>
       <c r="B67">
-        <v>0.0012137221618925653</v>
+        <v>0.0016459156319821237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.03045933185055676</v>
       </c>
       <c r="B68">
-        <v>0.0011383353829454508</v>
+        <v>0.0015678989887007314</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.028283665289802702</v>
       </c>
       <c r="B69">
-        <v>0.0010372636579912933</v>
+        <v>0.001466705942508528</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.026107998729048652</v>
       </c>
       <c r="B70">
-        <v>0.00092268745082250384</v>
+        <v>0.001351467816615913</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.023932332168294598</v>
       </c>
       <c r="B71">
-        <v>0.00080788685604787</v>
+        <v>0.0012321402875751586</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.02175666560754054</v>
       </c>
       <c r="B72">
-        <v>0.00068955206245808706</v>
+        <v>0.0011062357221737036</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.019580999046786486</v>
       </c>
       <c r="B73">
-        <v>0.000562164759866344</v>
+        <v>0.00096960968755496855</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.017405332486032432</v>
       </c>
       <c r="B74">
-        <v>0.00042796254799389857</v>
+        <v>0.00082393386205113642</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.01522966592527838</v>
       </c>
       <c r="B75">
-        <v>0.00029116368017457182</v>
+        <v>0.00067236499767760183</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.013053999364524326</v>
       </c>
       <c r="B76">
-        <v>0.00015615311428436872</v>
+        <v>0.00051818402999384322</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.01087833280377027</v>
       </c>
       <c r="B77">
-        <v>2.6987240340079291E-05</v>
+        <v>0.00036442503381637514</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0087026662430162161</v>
       </c>
       <c r="B78">
-        <v>-9.37585276205485E-05</v>
+        <v>0.00021301045744577315</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0065269996822621629</v>
       </c>
       <c r="B79">
-        <v>-0.00020167385211653991</v>
+        <v>6.7238534792661269E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.004351333121508108</v>
       </c>
       <c r="B80">
-        <v>-0.0002890000304355687</v>
+        <v>-6.70820412386551E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.002175666560754054</v>
       </c>
       <c r="B81">
-        <v>-0.00033663507325676746</v>
+        <v>-0.0001756357477609674</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.002433523354040866</v>
       </c>
       <c r="B2">
-        <v>0.000709148955679403</v>
+        <v>0.000529068227480379</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.004867046708081732</v>
       </c>
       <c r="B3">
-        <v>0.0010737712428744498</v>
+        <v>0.00082555186076228187</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.007300570062122598</v>
       </c>
       <c r="B4">
-        <v>0.0013829755487331944</v>
+        <v>0.0010821920621737434</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.009734093416163464</v>
       </c>
       <c r="B5">
-        <v>0.001652828903080065</v>
+        <v>0.001309702110160303</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.012167616770204328</v>
       </c>
       <c r="B6">
-        <v>0.0018898801310620547</v>
+        <v>0.0015124497077733036</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.014601140124245196</v>
       </c>
       <c r="B7">
-        <v>0.0020978660057583576</v>
+        <v>0.0016929277196459577</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.017034663478286062</v>
       </c>
       <c r="B8">
-        <v>0.002278982430514092</v>
+        <v>0.0018526016948496819</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.019468186832326928</v>
       </c>
       <c r="B9">
-        <v>0.0024366642230435639</v>
+        <v>0.001993762972608126</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.021901710186367791</v>
       </c>
       <c r="B10">
-        <v>0.0025746201492558435</v>
+        <v>0.0021188854494164936</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B11">
-        <v>0.0026964158534698766</v>
+        <v>0.0022303474607039703</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.026768756894449526</v>
       </c>
       <c r="B12">
-        <v>0.0028039538158489809</v>
+        <v>0.0023294184930760793</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.029202280248490392</v>
       </c>
       <c r="B13">
-        <v>0.0028926269815240848</v>
+        <v>0.002413028198909711</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.031635803602531258</v>
       </c>
       <c r="B14">
-        <v>0.0029596793278736963</v>
+        <v>0.0024793401769041879</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.034069326956572124</v>
       </c>
       <c r="B15">
-        <v>0.0030162684962990287</v>
+        <v>0.0025357936452772</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.036502850310612983</v>
       </c>
       <c r="B16">
-        <v>0.0030726282218508519</v>
+        <v>0.0025892118188509451</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.038936373664653856</v>
       </c>
       <c r="B17">
-        <v>0.0031213829501554619</v>
+        <v>0.0026346782793472893</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.041369897018694722</v>
       </c>
       <c r="B18">
-        <v>0.00315300876548945</v>
+        <v>0.0026658442805733945</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.043803420372735581</v>
       </c>
       <c r="B19">
-        <v>0.003166997596155068</v>
+        <v>0.0026823713977779449</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.046236943726776454</v>
       </c>
       <c r="B20">
-        <v>0.0031650953314609834</v>
+        <v>0.0026854237865700055</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B21">
-        <v>0.0031490478607158609</v>
+        <v>0.00267616560255864</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.051103990434858179</v>
       </c>
       <c r="B22">
-        <v>0.0031202903001497835</v>
+        <v>0.0026555537442617054</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.053537513788899052</v>
       </c>
       <c r="B23">
-        <v>0.0030790146736784916</v>
+        <v>0.0026237160818322262</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.055971037142939918</v>
       </c>
       <c r="B24">
-        <v>0.00302510223213914</v>
+        <v>0.0025805732283320205</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.058404560496980784</v>
       </c>
       <c r="B25">
-        <v>0.0029584342263688852</v>
+        <v>0.0025260457968229043</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.060838083851021643</v>
       </c>
       <c r="B26">
-        <v>0.0028788406777948737</v>
+        <v>0.0024600201752044181</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.063271607205062516</v>
       </c>
       <c r="B27">
-        <v>0.0027859466902042142</v>
+        <v>0.0023822458507269874</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.065705130559103375</v>
       </c>
       <c r="B28">
-        <v>0.0026793261379740078</v>
+        <v>0.002292438085478762</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.068138653913144248</v>
       </c>
       <c r="B29">
-        <v>0.0025585528954813535</v>
+        <v>0.0021903121415478904</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.070572177267185107</v>
       </c>
       <c r="B30">
-        <v>0.0024234323206719617</v>
+        <v>0.0020757375306427969</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.073005700621225966</v>
       </c>
       <c r="B31">
-        <v>0.0022746957057659762</v>
+        <v>0.0019492007629530103</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.075439223975266839</v>
       </c>
       <c r="B32">
-        <v>0.0021133058265521473</v>
+        <v>0.0018113425982883328</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.077872747329307712</v>
       </c>
       <c r="B33">
-        <v>0.0019402254588192273</v>
+        <v>0.0016628037964585684</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.080306270683348571</v>
       </c>
       <c r="B34">
-        <v>0.0017560432716642205</v>
+        <v>0.0015039756373967821</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.082739794037389444</v>
       </c>
       <c r="B35">
-        <v>0.0015598515074171362</v>
+        <v>0.0013342514815290851</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.0851733173914303</v>
       </c>
       <c r="B36">
-        <v>0.0013503683017162373</v>
+        <v>0.0011527752094048502</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.087606840745471162</v>
       </c>
       <c r="B37">
-        <v>0.0011263117901997835</v>
+        <v>0.00095869070157344864</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.090040364099512035</v>
       </c>
       <c r="B38">
-        <v>0.00088548268040066749</v>
+        <v>0.00075053015226919683</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.092473887453552908</v>
       </c>
       <c r="B39">
-        <v>0.00062201196743030254</v>
+        <v>0.00052437901046618331</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.094907410807593767</v>
       </c>
       <c r="B40">
-        <v>0.0003291132182947317</v>
+        <v>0.0002757110388234399</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.094907410807593767</v>
       </c>
       <c r="B43">
-        <v>8.7001414669807026E-06</v>
+        <v>6.2102320938272549E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.092473887453552908</v>
       </c>
       <c r="B44">
-        <v>3.6214225645586494E-05</v>
+        <v>0.00013384718260970585</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.090040364099512035</v>
       </c>
       <c r="B45">
-        <v>7.5767511611842688E-05</v>
+        <v>0.00021072003974331353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.087606840745471162</v>
       </c>
       <c r="B46">
-        <v>0.00012058525844177461</v>
+        <v>0.00028820634706810938</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.0851733173914303</v>
       </c>
       <c r="B47">
-        <v>0.00016480974784791554</v>
+        <v>0.00036240284015930243</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.082739794037389444</v>
       </c>
       <c r="B48">
-        <v>0.00020625135208883036</v>
+        <v>0.00043185137797688121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.080306270683348571</v>
       </c>
       <c r="B49">
-        <v>0.00024363746605959256</v>
+        <v>0.00049570510032703036</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.077872747329307712</v>
       </c>
       <c r="B50">
-        <v>0.000275695484655275</v>
+        <v>0.0005531171470159336</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.075439223975266839</v>
       </c>
       <c r="B51">
-        <v>0.00030152645696926173</v>
+        <v>0.00060348968523307582</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.073005700621225966</v>
       </c>
       <c r="B52">
-        <v>0.00032172604888818076</v>
+        <v>0.00064722099170114655</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.070572177267185107</v>
       </c>
       <c r="B53">
-        <v>0.0003372635804969711</v>
+        <v>0.00068495837052613619</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.068138653913144248</v>
       </c>
       <c r="B54">
-        <v>0.00034910837188057179</v>
+        <v>0.00071734912581403534</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.065705130559103375</v>
       </c>
       <c r="B55">
-        <v>0.00035799782300253345</v>
+        <v>0.00074488587549777913</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.063271607205062516</v>
       </c>
       <c r="B56">
-        <v>0.00036374165334085293</v>
+        <v>0.00076744249281807976</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.060838083851021643</v>
       </c>
       <c r="B57">
-        <v>0.00036591766225213887</v>
+        <v>0.00078473816484259475</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.058404560496980784</v>
       </c>
       <c r="B58">
-        <v>0.00036410364909299973</v>
+        <v>0.00079649207863898073</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.055971037142939918</v>
       </c>
       <c r="B59">
-        <v>0.00035792820929642181</v>
+        <v>0.00080245721310354156</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.053537513788899052</v>
       </c>
       <c r="B60">
-        <v>0.000347223122600902</v>
+        <v>0.000802521714447167</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.051103990434858179</v>
       </c>
       <c r="B61">
-        <v>0.00033187096482131492</v>
+        <v>0.0007966075207093931</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B62">
-        <v>0.00031175431177253522</v>
+        <v>0.00078463656992975618</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.046236943726776454</v>
       </c>
       <c r="B63">
-        <v>0.00028706606211511632</v>
+        <v>0.000766737607006094</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.043803420372735581</v>
       </c>
       <c r="B64">
-        <v>0.00025924040589232658</v>
+        <v>0.00074386660426945016</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.041369897018694722</v>
       </c>
       <c r="B65">
-        <v>0.00023002185599311324</v>
+        <v>0.00071718634090916936</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.038936373664653856</v>
       </c>
       <c r="B66">
-        <v>0.00020115492530642335</v>
+        <v>0.00068785959611459646</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.036502850310612983</v>
       </c>
       <c r="B67">
-        <v>0.00017212980385141098</v>
+        <v>0.00065554620685131777</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.034069326956572124</v>
       </c>
       <c r="B68">
-        <v>0.00013341939016805763</v>
+        <v>0.00061389424118988613</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.031635803602531258</v>
       </c>
       <c r="B69">
-        <v>7.7644422056646513E-05</v>
+        <v>0.0005579835730261547</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.029202280248490392</v>
       </c>
       <c r="B70">
-        <v>1.5034285837842E-05</v>
+        <v>0.00049463306845221576</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.026768756894449526</v>
       </c>
       <c r="B71">
-        <v>-4.325812078842831E-05</v>
+        <v>0.00043127720198447313</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B72">
-        <v>-9.9994503125562634E-05</v>
+        <v>0.00036607388964034383</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.021901710186367791</v>
       </c>
       <c r="B73">
-        <v>-0.00015978804978025566</v>
+        <v>0.00029594665005909412</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.019468186832326928</v>
       </c>
       <c r="B74">
-        <v>-0.00022074327956906164</v>
+        <v>0.00022215797086637594</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.017034663478286062</v>
       </c>
       <c r="B75">
-        <v>-0.00027930198347236884</v>
+        <v>0.00014707875219204138</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.014601140124245196</v>
       </c>
       <c r="B76">
-        <v>-0.00033176371091604283</v>
+        <v>7.3174575196357315E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.012167616770204328</v>
       </c>
       <c r="B77">
-        <v>-0.00037470240867045314</v>
+        <v>2.72801461829823E-06</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.009734093416163464</v>
       </c>
       <c r="B78">
-        <v>-0.00040593185443850687</v>
+        <v>-6.2805061518744965E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.007300570062122598</v>
       </c>
       <c r="B79">
-        <v>-0.00042172537062351155</v>
+        <v>-0.00012094188406406061</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.004867046708081732</v>
       </c>
       <c r="B80">
-        <v>-0.00041554504979855945</v>
+        <v>-0.0001673256676863913</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.002433523354040866</v>
       </c>
       <c r="B81">
-        <v>-0.00037133541351474126</v>
+        <v>-0.00019125468531571728</v>
       </c>
     </row>
     <row r="82" spans="1:2">
